--- a/JsonConverter/ExcelFiles/DropObject.xlsx
+++ b/JsonConverter/ExcelFiles/DropObject.xlsx
@@ -79,7 +79,7 @@
     <t xml:space="preserve">10,500</t>
   </si>
   <si>
-    <t xml:space="preserve">Item_Gold_0001</t>
+    <t xml:space="preserve">Gold_0001</t>
   </si>
   <si>
     <t xml:space="preserve">Icon/Icon_Item_Gold_0001</t>
@@ -100,7 +100,7 @@
     <t xml:space="preserve">1,5</t>
   </si>
   <si>
-    <t xml:space="preserve">Item_Fuel_0002</t>
+    <t xml:space="preserve">Fuel_0002</t>
   </si>
   <si>
     <t xml:space="preserve">Icon/Icon_Item_Fuel_0002</t>
@@ -147,7 +147,7 @@
     <t xml:space="preserve">드랍된 보급품</t>
   </si>
   <si>
-    <t xml:space="preserve">Item_Supplies_0003</t>
+    <t xml:space="preserve">Supplies_0003</t>
   </si>
   <si>
     <r>
@@ -213,7 +213,7 @@
     <t xml:space="preserve">드랍된 교역품 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Item_TradingGoods_0004</t>
+    <t xml:space="preserve">TradingGoods_0004</t>
   </si>
   <si>
     <r>
@@ -279,7 +279,7 @@
     <t xml:space="preserve">드랍된 교역품 2</t>
   </si>
   <si>
-    <t xml:space="preserve">Item_TradingGoods_0005</t>
+    <t xml:space="preserve">TradingGoods_0005</t>
   </si>
   <si>
     <t xml:space="preserve">Icon/Icon_Item_TradingGoods_0005</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">드랍된 교역품 3</t>
   </si>
   <si>
-    <t xml:space="preserve">Item_TradingGoods_0006</t>
+    <t xml:space="preserve">TradingGoods_0006</t>
   </si>
   <si>
     <t xml:space="preserve">Icon/Icon_Item_TradingGoods_0006</t>
@@ -373,7 +373,7 @@
     <t xml:space="preserve">드랍된 교역품 4</t>
   </si>
   <si>
-    <t xml:space="preserve">Item_TradingGoods_0007</t>
+    <t xml:space="preserve">TradingGoods_0007</t>
   </si>
   <si>
     <t xml:space="preserve">Icon/Icon_Item_TradingGoods_0007</t>
@@ -513,44 +513,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -558,36 +530,52 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -845,7 +833,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.27"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="46.54"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="2" width="46.54"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="31.91"/>
@@ -931,7 +919,7 @@
       <c r="B4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -940,133 +928,133 @@
       <c r="E4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="10" t="s">
         <v>21</v>
       </c>
       <c r="I4" s="3"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12"/>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="11" t="s">
         <v>22</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="12"/>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="12"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="11" t="s">
         <v>35</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12"/>
-      <c r="N7" s="12"/>
-      <c r="O7" s="12"/>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="12"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
@@ -1075,34 +1063,34 @@
       <c r="B8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="12"/>
-      <c r="N8" s="12"/>
-      <c r="O8" s="12"/>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="12"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
@@ -1111,34 +1099,34 @@
       <c r="B9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="12"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
@@ -1147,268 +1135,268 @@
       <c r="B10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="H10" s="17" t="s">
+      <c r="H10" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="12"/>
-      <c r="N10" s="12"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
-      <c r="D11" s="18"/>
+      <c r="D11" s="14"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="12"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="12"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="16"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="14"/>
       <c r="F12" s="4"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12"/>
-      <c r="O12" s="12"/>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="16"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="14"/>
       <c r="F13" s="4"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="12"/>
-      <c r="O13" s="12"/>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="12"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="16"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="14"/>
       <c r="F14" s="4"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="12"/>
-      <c r="P14" s="12"/>
-      <c r="Q14" s="12"/>
-      <c r="R14" s="12"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="16"/>
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="14"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="12"/>
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="12"/>
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="F19" s="12"/>
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="F19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="F20" s="12"/>
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="F20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="F21" s="12"/>
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="F21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="12"/>
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="12"/>
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="12"/>
-      <c r="H24" s="12"/>
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="10"/>
+      <c r="H24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="12"/>
-      <c r="H25" s="12"/>
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="10"/>
+      <c r="H25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="12"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="12"/>
-      <c r="H26" s="12"/>
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="10"/>
+      <c r="H26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="12"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="12"/>
-      <c r="H27" s="12"/>
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="10"/>
+      <c r="H27" s="10"/>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="12"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="16"/>
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="14"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="16"/>
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="14"/>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="12"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="16"/>
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="14"/>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="12"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="16"/>
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="14"/>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="12"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="16"/>
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="14"/>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="12"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="16"/>
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="14"/>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="12"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
+      <c r="A34" s="10"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/JsonConverter/ExcelFiles/DropObject.xlsx
+++ b/JsonConverter/ExcelFiles/DropObject.xlsx
@@ -20,9 +20,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="59">
-  <si>
-    <t xml:space="preserve">캐릭터 고유 ID</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="55">
+  <si>
+    <t xml:space="preserve">고유 ID</t>
   </si>
   <si>
     <t xml:space="preserve">몬스터 설명 (도감용)</t>
@@ -37,9 +37,6 @@
     <t xml:space="preserve">string</t>
   </si>
   <si>
-    <t xml:space="preserve">int[]</t>
-  </si>
-  <si>
     <t xml:space="preserve">Id</t>
   </si>
   <si>
@@ -52,9 +49,6 @@
     <t xml:space="preserve">Description</t>
   </si>
   <si>
-    <t xml:space="preserve">DropCountRange</t>
-  </si>
-  <si>
     <t xml:space="preserve">DropItemDataId</t>
   </si>
   <si>
@@ -76,9 +70,6 @@
     <t xml:space="preserve">드랍된 화폐</t>
   </si>
   <si>
-    <t xml:space="preserve">10,500</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gold_0001</t>
   </si>
   <si>
@@ -95,9 +86,6 @@
   </si>
   <si>
     <t xml:space="preserve">드랍된 연료</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,5</t>
   </si>
   <si>
     <t xml:space="preserve">Fuel_0002</t>
@@ -513,7 +501,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -559,10 +547,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -835,11 +819,13 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="46.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="2" width="46.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="31.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="39.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="24.35"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="1" width="11.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="46.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="31.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="39.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="24.35"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="17" min="9" style="1" width="11.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16383" min="19" style="1" width="11.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -852,9 +838,8 @@
         <v>1</v>
       </c>
       <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5" t="s">
+      <c r="F1" s="5"/>
+      <c r="G1" s="5" t="s">
         <v>2</v>
       </c>
     </row>
@@ -872,72 +857,65 @@
         <v>4</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I2" s="3"/>
+      <c r="H2" s="3"/>
     </row>
     <row r="3" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="F3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="G3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="R3" s="0"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="F4" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="G4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="10"/>
       <c r="J4" s="10"/>
       <c r="K4" s="10"/>
       <c r="L4" s="10"/>
@@ -946,33 +924,30 @@
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
       <c r="Q4" s="10"/>
-      <c r="R4" s="10"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="F5" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="G5" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>28</v>
-      </c>
+      <c r="H5" s="10"/>
       <c r="I5" s="10"/>
       <c r="J5" s="10"/>
       <c r="K5" s="10"/>
@@ -982,33 +957,30 @@
       <c r="O5" s="10"/>
       <c r="P5" s="10"/>
       <c r="Q5" s="10"/>
-      <c r="R5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="G6" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>34</v>
-      </c>
+      <c r="H6" s="10"/>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
@@ -1018,33 +990,30 @@
       <c r="O6" s="10"/>
       <c r="P6" s="10"/>
       <c r="Q6" s="10"/>
-      <c r="R6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="13" t="s">
+      <c r="G7" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>40</v>
-      </c>
+      <c r="H7" s="10"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
@@ -1054,33 +1023,30 @@
       <c r="O7" s="10"/>
       <c r="P7" s="10"/>
       <c r="Q7" s="10"/>
-      <c r="R7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="13" t="s">
+      <c r="G8" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>46</v>
-      </c>
+      <c r="H8" s="10"/>
       <c r="I8" s="10"/>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
@@ -1090,33 +1056,30 @@
       <c r="O8" s="10"/>
       <c r="P8" s="10"/>
       <c r="Q8" s="10"/>
-      <c r="R8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="13" t="s">
+      <c r="G9" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>52</v>
-      </c>
+      <c r="H9" s="10"/>
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
@@ -1126,33 +1089,30 @@
       <c r="O9" s="10"/>
       <c r="P9" s="10"/>
       <c r="Q9" s="10"/>
-      <c r="R9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="13" t="s">
+      <c r="G10" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>58</v>
-      </c>
+      <c r="H10" s="10"/>
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
       <c r="K10" s="10"/>
@@ -1162,15 +1122,14 @@
       <c r="O10" s="10"/>
       <c r="P10" s="10"/>
       <c r="Q10" s="10"/>
-      <c r="R10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
-      <c r="D11" s="14"/>
+      <c r="D11" s="13"/>
       <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
+      <c r="F11" s="10"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
@@ -1182,15 +1141,14 @@
       <c r="O11" s="10"/>
       <c r="P11" s="10"/>
       <c r="Q11" s="10"/>
-      <c r="R11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="4"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="10"/>
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
       <c r="I12" s="10"/>
@@ -1202,15 +1160,14 @@
       <c r="O12" s="10"/>
       <c r="P12" s="10"/>
       <c r="Q12" s="10"/>
-      <c r="R12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="4"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="10"/>
       <c r="G13" s="10"/>
       <c r="H13" s="10"/>
       <c r="I13" s="10"/>
@@ -1222,15 +1179,14 @@
       <c r="O13" s="10"/>
       <c r="P13" s="10"/>
       <c r="Q13" s="10"/>
-      <c r="R13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="4"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="10"/>
       <c r="G14" s="10"/>
       <c r="H14" s="10"/>
       <c r="I14" s="10"/>
@@ -1242,155 +1198,139 @@
       <c r="O14" s="10"/>
       <c r="P14" s="10"/>
       <c r="Q14" s="10"/>
-      <c r="R14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="14"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
-      <c r="C16" s="14"/>
+      <c r="C16" s="13"/>
       <c r="D16" s="3"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="10"/>
+      <c r="E16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10"/>
       <c r="B17" s="10"/>
-      <c r="C17" s="14"/>
+      <c r="C17" s="13"/>
       <c r="D17" s="3"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="10"/>
+      <c r="E17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="10"/>
       <c r="B18" s="10"/>
-      <c r="C18" s="14"/>
+      <c r="C18" s="13"/>
       <c r="D18" s="3"/>
-      <c r="E18" s="14"/>
+      <c r="E18" s="10"/>
       <c r="F18" s="10"/>
       <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10"/>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
-      <c r="F19" s="10"/>
+      <c r="E19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="10"/>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
-      <c r="F20" s="10"/>
+      <c r="E20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="10"/>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
       <c r="D21" s="10"/>
-      <c r="F21" s="10"/>
+      <c r="E21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="10"/>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
       <c r="D22" s="3"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="10"/>
+      <c r="E22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="10"/>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
       <c r="D23" s="3"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="10"/>
+      <c r="E23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="10"/>
       <c r="D24" s="3"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="10"/>
-      <c r="H24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="G24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="10"/>
       <c r="D25" s="3"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="10"/>
-      <c r="H25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="G25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
       <c r="D26" s="3"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="10"/>
-      <c r="H26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="G26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="10"/>
       <c r="D27" s="3"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="10"/>
-      <c r="H27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="G27" s="10"/>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
       <c r="D28" s="3"/>
-      <c r="E28" s="14"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="10"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="14"/>
+      <c r="D29" s="12"/>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="10"/>
       <c r="B30" s="10"/>
       <c r="C30" s="10"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="14"/>
+      <c r="D30" s="12"/>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="10"/>
       <c r="B31" s="10"/>
       <c r="C31" s="10"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="14"/>
+      <c r="D31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="10"/>
       <c r="B32" s="10"/>
       <c r="C32" s="10"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="14"/>
+      <c r="D32" s="12"/>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="14"/>
+      <c r="D33" s="12"/>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="10"/>
